--- a/ML_dec_tree_football/pics/taulukot_ML.xlsx
+++ b/ML_dec_tree_football/pics/taulukot_ML.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9288cc8461a4b73d/python_projektit/ML_dec_tree_football/pics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{CBE297D0-A694-45AF-A00D-2522D04020B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DDA8298-17D3-4CCD-8F2D-3270B44AAA87}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{CBE297D0-A694-45AF-A00D-2522D04020B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{056D8BEC-DCCC-463F-AC40-4DB4E72A5889}"/>
   <bookViews>
-    <workbookView xWindow="1208" yWindow="1132" windowWidth="19747" windowHeight="10020" activeTab="1" xr2:uid="{746D1673-98AC-41AA-B843-C548F353FC7B}"/>
+    <workbookView xWindow="727" yWindow="1065" windowWidth="18848" windowHeight="10148" activeTab="1" xr2:uid="{746D1673-98AC-41AA-B843-C548F353FC7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Taul1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="14">
   <si>
     <t>Classification Report:</t>
   </si>
@@ -69,27 +69,6 @@
     <t>target</t>
   </si>
   <si>
-    <t>precision    recall  f1-score   support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           0      0.562     0.810     0.664       522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           1      0.111     0.004     0.007       269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           2      0.507     0.548     0.527       372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    accuracy                          0.540      1163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   macro avg      0.394     0.454     0.399      1163</t>
-  </si>
-  <si>
-    <t>weighted avg      0.440     0.540     0.468      1163</t>
-  </si>
-  <si>
     <t>XGboost</t>
   </si>
   <si>
@@ -106,7 +85,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,12 +94,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -143,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -594,51 +578,263 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="double">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normaali" xfId="0" builtinId="0"/>
@@ -973,351 +1169,334 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D39CE0-58CD-40F2-87C6-DEE5E390984B}">
-  <dimension ref="B1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:J16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="6" max="6" width="1.9296875" customWidth="1"/>
+    <col min="1" max="1" width="1.19921875" style="48" customWidth="1"/>
+    <col min="2" max="5" width="9.59765625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="1.9296875" style="48" customWidth="1"/>
+    <col min="7" max="10" width="9.59765625" style="48" customWidth="1"/>
+    <col min="11" max="11" width="1" style="48" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B2" s="29"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31" t="s">
+    <row r="1" spans="2:10" ht="13.15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B2" s="49"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="32"/>
-      <c r="L2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="36"/>
-    </row>
-    <row r="4" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="16" t="s">
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="52"/>
+    </row>
+    <row r="3" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="56"/>
+    </row>
+    <row r="4" spans="2:10" ht="13.9" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="2" t="s">
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="17"/>
-      <c r="L4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="18" t="s">
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="61"/>
+    </row>
+    <row r="5" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="34"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="L5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B6" s="20">
+    </row>
+    <row r="6" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B6" s="19">
         <v>0</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="20">
         <v>0.6</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="20">
         <v>0.7</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="21">
         <v>0.65</v>
       </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="7">
+      <c r="F6" s="54"/>
+      <c r="G6" s="22">
         <v>0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="20">
         <v>0.53900000000000003</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="20">
         <v>0.48499999999999999</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="23">
         <v>0.51100000000000001</v>
       </c>
-      <c r="L6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B7" s="20">
+    </row>
+    <row r="7" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="20">
         <v>0.24</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="20">
         <v>0.08</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="21">
         <v>0.12</v>
       </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="7">
+      <c r="F7" s="54"/>
+      <c r="G7" s="22">
         <v>1</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="20">
         <v>0.23200000000000001</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="20">
         <v>0.26800000000000002</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="23">
         <v>0.248</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B8" s="20">
+    <row r="8" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="20">
         <v>0.49</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="20">
         <v>0.63</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="21">
         <v>0.55000000000000004</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="7">
+      <c r="F8" s="54"/>
+      <c r="G8" s="22">
         <v>2</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="20">
         <v>0.39700000000000002</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="20">
         <v>0.40899999999999997</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="23">
         <v>0.40300000000000002</v>
       </c>
-      <c r="L8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="22" t="s">
+    </row>
+    <row r="9" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12">
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26">
         <v>0.53</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="54"/>
+      <c r="G9" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="23">
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="64">
         <v>0.41</v>
       </c>
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="33"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="36"/>
-      <c r="L10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="16" t="s">
+    </row>
+    <row r="10" spans="2:10" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="53"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="56"/>
+    </row>
+    <row r="11" spans="2:10" ht="13.9" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="2" t="s">
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="2:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="18" t="s">
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="61"/>
+    </row>
+    <row r="12" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B13" s="20">
+    <row r="13" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B13" s="19">
         <v>0</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="20">
         <v>0.55400000000000005</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="20">
         <v>0.81</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="21">
         <v>0.65800000000000003</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="7">
+      <c r="F13" s="54"/>
+      <c r="G13" s="22">
         <v>0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="20">
         <v>0.54</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="20">
         <v>0.54200000000000004</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="23">
         <v>0.54100000000000004</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B14" s="20">
+    <row r="14" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B14" s="19">
         <v>1</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="20">
         <v>0</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="20">
         <v>0</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="21">
         <v>0</v>
       </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="7">
+      <c r="F14" s="54"/>
+      <c r="G14" s="22">
         <v>1</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="20">
         <v>0.23599999999999999</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="20">
         <v>0.24199999999999999</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="23">
         <v>0.23899999999999999</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B15" s="20">
+    <row r="15" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B15" s="19">
         <v>2</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="20">
         <v>0.51500000000000001</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="20">
         <v>0.55400000000000005</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="21">
         <v>0.53400000000000003</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="7">
+      <c r="F15" s="54"/>
+      <c r="G15" s="22">
         <v>2</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="20">
         <v>0.40500000000000003</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="20">
         <v>0.39500000000000002</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="23">
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="25" t="s">
+    <row r="16" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27">
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44">
         <v>0.54100000000000004</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="28" t="s">
+      <c r="F16" s="67"/>
+      <c r="G16" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="38">
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="47">
         <v>0.42599999999999999</v>
       </c>
     </row>
@@ -1329,327 +1508,335 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620C27FD-E426-401F-9CB0-6FF3654CB049}">
-  <dimension ref="B1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:J16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="1.1328125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="9.59765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" style="1" customWidth="1"/>
+    <col min="7" max="9" width="9.59765625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="0.796875" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.06640625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B2" s="29"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31" t="s">
+    <row r="1" spans="2:10" ht="13.15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="32"/>
-    </row>
-    <row r="3" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="36"/>
-    </row>
-    <row r="4" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="17"/>
-    </row>
-    <row r="5" spans="2:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="18" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="2:10" ht="13.9" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="34"/>
-      <c r="G5" s="18" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="18" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B6" s="20">
+    <row r="6" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B6" s="19">
         <v>0</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="20">
         <v>0.56200000000000006</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="20">
         <v>0.81</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="21">
         <v>0.66400000000000003</v>
       </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="7">
+      <c r="F6" s="7"/>
+      <c r="G6" s="22">
         <v>0</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="20">
         <v>0.52800000000000002</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="20">
         <v>0.53800000000000003</v>
       </c>
-      <c r="J6" s="21">
+      <c r="J6" s="23">
         <v>0.53300000000000003</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B7" s="20">
+    <row r="7" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B7" s="19">
         <v>1</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="20">
         <v>0.111</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="20">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="21">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="7">
+      <c r="F7" s="7"/>
+      <c r="G7" s="22">
         <v>1</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="20">
         <v>0.24399999999999999</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="20">
         <v>0.23</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="23">
         <v>0.23699999999999999</v>
       </c>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B8" s="20">
+    </row>
+    <row r="8" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B8" s="19">
         <v>2</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="20">
         <v>0.50700000000000001</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="20">
         <v>0.54800000000000004</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="21">
         <v>0.52700000000000002</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="7">
+      <c r="F8" s="7"/>
+      <c r="G8" s="22">
         <v>2</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="20">
         <v>0.41399999999999998</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="20">
         <v>0.41899999999999998</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="23">
         <v>0.41699999999999998</v>
       </c>
     </row>
-    <row r="9" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12">
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26">
         <v>0.54</v>
       </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="10" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="39">
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="29">
         <v>0.42899999999999999</v>
       </c>
     </row>
-    <row r="10" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B10" s="33"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="36"/>
-    </row>
-    <row r="11" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="17"/>
-    </row>
-    <row r="12" spans="2:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="18" t="s">
+    <row r="10" spans="2:10" ht="13.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="2:10" ht="13.9" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="18" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="36" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B13" s="20">
+    <row r="13" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B13" s="15">
         <v>0</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="37">
         <v>0.56499999999999995</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="38">
         <v>0.79300000000000004</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="39">
         <v>0.66</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="7">
+      <c r="F13" s="7"/>
+      <c r="G13" s="22">
         <v>0</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="20">
         <v>0.51800000000000002</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="20">
         <v>0.53800000000000003</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="23">
         <v>0.52800000000000002</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B14" s="20">
+    <row r="14" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B14" s="19">
         <v>1</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="40">
         <v>0</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="20">
         <v>0</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="21">
         <v>0</v>
       </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="7">
+      <c r="F14" s="7"/>
+      <c r="G14" s="22">
         <v>1</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="20">
         <v>0.186</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="20">
         <v>0.17799999999999999</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="23">
         <v>0.182</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B15" s="20">
+    <row r="15" spans="2:10" ht="13.15" x14ac:dyDescent="0.4">
+      <c r="B15" s="19">
         <v>2</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="40">
         <v>0.503</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="20">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="21">
         <v>0.53900000000000003</v>
       </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="7">
+      <c r="F15" s="7"/>
+      <c r="G15" s="22">
         <v>2</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="20">
         <v>0.438</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="20">
         <v>0.42699999999999999</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="23">
         <v>0.433</v>
       </c>
     </row>
-    <row r="16" spans="2:13" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B16" s="25" t="s">
+    <row r="16" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27">
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44">
         <v>0.54200000000000004</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="28" t="s">
+      <c r="F16" s="45"/>
+      <c r="G16" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="38">
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="47">
         <v>0.42</v>
       </c>
     </row>
